--- a/(11.2) 호접지몽 작업 할당 및 계획표.xlsx
+++ b/(11.2) 호접지몽 작업 할당 및 계획표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82103\Documents\GitHub\SA-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFC224B-8C5E-42AA-B940-BC412C8C82C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED18A3A-B991-48D3-893D-C5AAB63957FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32565" yWindow="810" windowWidth="21435" windowHeight="14220" xr2:uid="{3658EF8A-7A19-440F-B1DD-92AC54D6A83E}"/>
+    <workbookView xWindow="33120" yWindow="630" windowWidth="20745" windowHeight="14220" xr2:uid="{3658EF8A-7A19-440F-B1DD-92AC54D6A83E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>그래픽</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,10 +163,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Main Scene to Title Script</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Title 버튼 Script</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,6 +179,18 @@
     <t>Event Scene 또는 
 Puzzle Scene 기획,
 Talking Event 기획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 맵 밖으로 안나가게 고정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -239,7 +247,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -288,16 +296,62 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -307,22 +361,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -659,296 +716,325 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D14B45-38B7-441E-9630-D07F05A4B61B}">
-  <dimension ref="B2:N19"/>
+  <dimension ref="B2:N22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="4"/>
+      <c r="K2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="1"/>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="2" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="6"/>
+      <c r="K3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="2" t="s">
+      <c r="L3" s="6"/>
+      <c r="M3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="3"/>
+      <c r="N3" s="6"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="2" t="s">
+      <c r="F7" s="8"/>
+      <c r="G7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2" t="s">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="K7:L10"/>
+    <mergeCell ref="G11:H14"/>
+    <mergeCell ref="I11:J14"/>
+    <mergeCell ref="K11:L14"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="M3:N6"/>
+    <mergeCell ref="M7:N10"/>
+    <mergeCell ref="M11:N14"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="K3:L6"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="B3:D6"/>
     <mergeCell ref="B7:D10"/>
@@ -962,22 +1048,6 @@
     <mergeCell ref="I3:J6"/>
     <mergeCell ref="G7:H10"/>
     <mergeCell ref="I7:J10"/>
-    <mergeCell ref="M3:N6"/>
-    <mergeCell ref="M7:N10"/>
-    <mergeCell ref="M11:N14"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="K3:L6"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="K7:L10"/>
-    <mergeCell ref="G11:H14"/>
-    <mergeCell ref="I11:J14"/>
-    <mergeCell ref="K11:L14"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="B18:D18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
